--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486293_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486293_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6553</v>
+        <v>6.4067</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0396</v>
+        <v>4.6985</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6157</v>
+        <v>1.7081</v>
       </c>
       <c r="G2" t="n">
         <v>4.4701</v>
@@ -610,13 +610,13 @@
         <v>0.6525</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4027</v>
+        <v>0.1541</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5622</v>
+        <v>0.2211</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1595</v>
+        <v>-0.067</v>
       </c>
       <c r="V2" t="n">
         <v>1.13</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9619</v>
+        <v>5.513</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6448</v>
+        <v>4.9801</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3171</v>
+        <v>0.5329</v>
       </c>
       <c r="G3" t="n">
         <v>5.1846</v>
@@ -688,13 +688,13 @@
         <v>0.6525</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8752</v>
+        <v>-0.3242</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.536</v>
+        <v>-0.2007</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3392</v>
+        <v>-0.1235</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X. OROZ URIA</t>
+          <t>A. KUNKEL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2603</v>
+        <v>3.8205</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5291</v>
+        <v>2.6322</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7311</v>
+        <v>1.1883</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8889</v>
+        <v>3.6468</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4841</v>
+        <v>0.7725</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4048</v>
+        <v>2.8743</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7981</v>
+        <v>2.5799</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2045</v>
+        <v>0.2618</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5937</v>
+        <v>2.3181</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0907</v>
+        <v>1.0669</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2796</v>
+        <v>0.5107</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1889</v>
+        <v>0.5562</v>
       </c>
       <c r="P4" t="n">
-        <v>0.87</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
         <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6286</v>
+        <v>-1.1086</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.399</v>
+        <v>-0.5552</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2297</v>
+        <v>-0.5534</v>
       </c>
       <c r="V4" t="n">
-        <v>1.13</v>
+        <v>1.4997</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>1.695</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. KAMBA</t>
+          <t>X. OROZ URIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0771</v>
+        <v>3.5647</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3918</v>
+        <v>2.8644</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6853</v>
+        <v>0.7003</v>
       </c>
       <c r="G5" t="n">
-        <v>2.9637</v>
+        <v>1.8889</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5233</v>
+        <v>1.4841</v>
       </c>
       <c r="I5" t="n">
-        <v>3.487</v>
+        <v>0.4048</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6793</v>
+        <v>1.7981</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6356000000000001</v>
+        <v>1.2045</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3149</v>
+        <v>0.5937</v>
       </c>
       <c r="M5" t="n">
-        <v>1.2844</v>
+        <v>0.0907</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1122</v>
+        <v>0.2796</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1722</v>
+        <v>-0.1889</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3304</v>
+        <v>-0.3242</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.548</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>1.8783</v>
+        <v>-0.2605</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.8695</v>
+        <v>1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7395</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. KUNKEL</t>
+          <t>T. BORG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0537</v>
+        <v>3.0951</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2969</v>
+        <v>1.4893</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7567</v>
+        <v>1.6058</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6468</v>
+        <v>1.1221</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7725</v>
+        <v>1.0735</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8743</v>
+        <v>0.0486</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5799</v>
+        <v>0.4513</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2618</v>
+        <v>1.0434</v>
       </c>
       <c r="L6" t="n">
-        <v>2.3181</v>
+        <v>-0.5921</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0669</v>
+        <v>0.6708</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5107</v>
+        <v>0.0302</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5562</v>
+        <v>0.6407</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.8754</v>
+        <v>0.1905</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8904</v>
+        <v>-0.2872</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9849</v>
+        <v>0.4777</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4997</v>
+        <v>1.13</v>
       </c>
       <c r="W6" t="n">
-        <v>1.695</v>
+        <v>1.3252</v>
       </c>
       <c r="X6" t="n">
         <v>-0.1952</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. BORG</t>
+          <t>J. VRANKIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6751</v>
+        <v>2.6496</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3776</v>
+        <v>0.6595</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2975</v>
+        <v>1.9901</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1221</v>
+        <v>0.4054</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0735</v>
+        <v>0.1918</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0486</v>
+        <v>0.2136</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4513</v>
+        <v>-0.53</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0434</v>
+        <v>0.1952</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5921</v>
+        <v>-0.7251</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6708</v>
+        <v>0.9354</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0302</v>
+        <v>-0.0033</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6407</v>
+        <v>0.9387</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6525</v>
+        <v>-0.435</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
         <v>0.6525</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2295</v>
+        <v>-0.1457</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.399</v>
+        <v>-0.548</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1694</v>
+        <v>0.4023</v>
       </c>
       <c r="V7" t="n">
-        <v>1.13</v>
+        <v>2.8249</v>
       </c>
       <c r="W7" t="n">
-        <v>1.3252</v>
+        <v>2.8249</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. VRANKIC</t>
+          <t>M. KAMBA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.6188</v>
+        <v>2.4067</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6595</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9593</v>
+        <v>1.7914</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4054</v>
+        <v>2.9637</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1918</v>
+        <v>-0.5233</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2136</v>
+        <v>3.487</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.53</v>
+        <v>1.6793</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1952</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7251</v>
+        <v>2.3149</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9354</v>
+        <v>1.2844</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0033</v>
+        <v>0.1122</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9387</v>
+        <v>1.1722</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1765</v>
+        <v>0.66</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.548</v>
+        <v>-0.3245</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3714</v>
+        <v>0.9845</v>
       </c>
       <c r="V8" t="n">
-        <v>2.8249</v>
+        <v>-1.8695</v>
       </c>
       <c r="W8" t="n">
-        <v>2.8249</v>
+        <v>-0.7395</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. GONZALEZ CALVO</t>
+          <t>I. JAKOVICS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8453</v>
+        <v>1.3687</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5195</v>
+        <v>-0.3184</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3258</v>
+        <v>1.687</v>
       </c>
       <c r="G9" t="n">
-        <v>0.607</v>
+        <v>1.0825</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.295</v>
+        <v>2.8101</v>
       </c>
       <c r="I9" t="n">
-        <v>0.902</v>
+        <v>-1.7276</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0201</v>
+        <v>0.5137</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7086</v>
+        <v>2.1169</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6885</v>
+        <v>-1.6032</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6271</v>
+        <v>0.5688</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4136</v>
+        <v>0.6932</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2136</v>
+        <v>-0.1243</v>
       </c>
       <c r="P9" t="n">
-        <v>0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R9" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8032</v>
+        <v>-0.2566</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5396</v>
+        <v>-0.5047</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2636</v>
+        <v>0.2481</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. JAKOVICS</t>
+          <t>J. GONZALEZ CALVO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.072</v>
+        <v>1.325</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4301</v>
+        <v>0.1842</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5021</v>
+        <v>1.1408</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0825</v>
+        <v>0.607</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8101</v>
+        <v>-0.295</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.7276</v>
+        <v>0.902</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5137</v>
+        <v>-0.0201</v>
       </c>
       <c r="K10" t="n">
-        <v>2.1169</v>
+        <v>-0.7086</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.6032</v>
+        <v>0.6885</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5688</v>
+        <v>0.6271</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6932</v>
+        <v>0.4136</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1243</v>
+        <v>0.2136</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5533</v>
+        <v>0.283</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6165</v>
+        <v>0.2043</v>
       </c>
       <c r="U10" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.384</v>
+        <v>-0.6614</v>
       </c>
       <c r="E11" t="n">
         <v>-1.5337</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1497</v>
+        <v>0.8723</v>
       </c>
       <c r="G11" t="n">
         <v>0.2531</v>
@@ -1312,13 +1312,13 @@
         <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0275</v>
+        <v>-0.3049</v>
       </c>
       <c r="T11" t="n">
         <v>-0.4675</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4399</v>
+        <v>0.1625</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1745</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0674</v>
+        <v>-0.8824</v>
       </c>
       <c r="E12" t="n">
         <v>-0.6088</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4586</v>
+        <v>-0.2736</v>
       </c>
       <c r="G12" t="n">
         <v>0.0028</v>
@@ -1390,13 +1390,13 @@
         <v>0.2175</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7227</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>-0.6165</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1062</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5649999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.8718</v>
+        <v>-4.7099</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.4769</v>
+        <v>-4.2534</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3949</v>
+        <v>-0.4565</v>
       </c>
       <c r="G13" t="n">
         <v>1.3463</v>
@@ -1468,13 +1468,13 @@
         <v>0.435</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2382</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.548</v>
+        <v>-0.3245</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3098</v>
+        <v>0.2481</v>
       </c>
       <c r="V13" t="n">
         <v>-2.0647</v>
@@ -1507,7 +1507,7 @@
         <v>11.4093</v>
       </c>
       <c r="F14" t="n">
-        <v>12.4868</v>
+        <v>12.4869</v>
       </c>
       <c r="G14" t="n">
         <v>22.9733</v>
@@ -1528,7 +1528,7 @@
         <v>8.793600000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>9.433399999999999</v>
+        <v>9.433400000000001</v>
       </c>
       <c r="N14" t="n">
         <v>3.4494</v>
@@ -1543,19 +1543,19 @@
         <v>-8.700099999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>7.6125</v>
+        <v>7.612499999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.7906</v>
+        <v>-1.7907</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.4671</v>
+        <v>-3.467100000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6761</v>
+        <v>1.6762</v>
       </c>
       <c r="V14" t="n">
-        <v>3.801099999999998</v>
+        <v>3.8011</v>
       </c>
       <c r="W14" t="n">
         <v>10.0367</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. VICEDO AYALA</t>
+          <t>E. WEMBI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6133</v>
+        <v>1.9341</v>
       </c>
       <c r="E15" t="n">
-        <v>1.832</v>
+        <v>2.091</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7813</v>
+        <v>-0.157</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0391</v>
+        <v>0.541</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3953</v>
+        <v>1.2773</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3562</v>
+        <v>-0.7363</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8983</v>
+        <v>1.9962</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5141</v>
+        <v>1.8432</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3841</v>
+        <v>0.153</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8592</v>
+        <v>-1.4552</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1188</v>
+        <v>-0.5659</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7403</v>
+        <v>-0.8893</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0347</v>
+        <v>0.2626</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9337</v>
+        <v>-0.2956</v>
       </c>
       <c r="U15" t="n">
-        <v>1.101</v>
+        <v>0.5582</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.113</v>
+        <v>-0.1745</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.113</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. WEMBI</t>
+          <t>E. VICEDO AYALA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9815</v>
+        <v>1.6217</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9793</v>
+        <v>0.9379</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0023</v>
+        <v>0.6838</v>
       </c>
       <c r="G16" t="n">
-        <v>0.541</v>
+        <v>0.0391</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2773</v>
+        <v>0.3953</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7363</v>
+        <v>-0.3562</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9962</v>
+        <v>0.8983</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8432</v>
+        <v>0.5141</v>
       </c>
       <c r="L16" t="n">
-        <v>0.153</v>
+        <v>0.3841</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4552</v>
+        <v>-0.8592</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5659</v>
+        <v>-0.1188</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8893</v>
+        <v>-0.7403</v>
       </c>
       <c r="P16" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S16" t="n">
-        <v>0.31</v>
+        <v>1.0431</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4074</v>
+        <v>0.0397</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7174</v>
+        <v>1.0034</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1745</v>
+        <v>-0.113</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.084</v>
+        <v>1.0634</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6213</v>
+        <v>0.1742</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4627</v>
+        <v>0.8891</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4924</v>
@@ -1780,13 +1780,13 @@
         <v>1.0875</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4746</v>
+        <v>0.4539</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5432</v>
+        <v>0.0961</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.06859999999999999</v>
+        <v>0.3578</v>
       </c>
       <c r="V17" t="n">
         <v>3.2769</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2385</v>
+        <v>0.0775</v>
       </c>
       <c r="E18" t="n">
-        <v>0.343</v>
+        <v>0.5665</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5815</v>
+        <v>-0.489</v>
       </c>
       <c r="G18" t="n">
         <v>-2.5721</v>
@@ -1858,13 +1858,13 @@
         <v>0.2175</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1438</v>
+        <v>0.1721</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2055</v>
+        <v>0.018</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0616</v>
+        <v>0.1541</v>
       </c>
       <c r="V18" t="n">
         <v>2.2599</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8697</v>
+        <v>-1.7194</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8878</v>
+        <v>-0.5525</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9819</v>
+        <v>-1.1669</v>
       </c>
       <c r="G19" t="n">
         <v>-1.9742</v>
@@ -1936,13 +1936,13 @@
         <v>0.2175</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0822</v>
+        <v>0.2325</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3305</v>
+        <v>0.0048</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4127</v>
+        <v>0.2277</v>
       </c>
       <c r="V19" t="n">
         <v>-0.1952</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.8663</v>
+        <v>-3.6363</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1564</v>
+        <v>-2.0446</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7099</v>
+        <v>-1.5917</v>
       </c>
       <c r="G20" t="n">
         <v>-2.6067</v>
@@ -2014,13 +2014,13 @@
         <v>1.5225</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.214</v>
+        <v>0.0159</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6249</v>
+        <v>-0.5131</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4108</v>
+        <v>0.529</v>
       </c>
       <c r="V20" t="n">
         <v>-2.5682</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. GALETTE</t>
+          <t>V. ARTEAGA GONZALEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8829</v>
+        <v>-4.8524</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3651</v>
+        <v>-2.1856</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.5178</v>
+        <v>-2.6668</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.6886</v>
+        <v>-1.1864</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2949</v>
+        <v>0.3133</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.3938</v>
+        <v>-1.4997</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8398</v>
+        <v>0.0663</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5356</v>
+        <v>0.6966</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3754</v>
+        <v>-0.6303</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8488</v>
+        <v>-1.2528</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8304</v>
+        <v>-0.3834</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0184</v>
+        <v>-0.8694</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S21" t="n">
-        <v>1.8259</v>
+        <v>0.447</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5622</v>
+        <v>-0.0769</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2636</v>
+        <v>0.5239</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.0202</v>
+        <v>-2.3729</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.0202</v>
+        <v>-2.3729</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V. ARTEAGA GONZALEZ</t>
+          <t>N. GALETTE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.7291</v>
+        <v>-5.2972</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1856</v>
+        <v>-1.5944</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5435</v>
+        <v>-3.7027</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1864</v>
+        <v>-2.6886</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3133</v>
+        <v>-0.2949</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4997</v>
+        <v>-2.3938</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0663</v>
+        <v>-0.8398</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6966</v>
+        <v>0.5356</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6303</v>
+        <v>-1.3754</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2528</v>
+        <v>-1.8488</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3834</v>
+        <v>-0.8304</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8694</v>
+        <v>-1.0184</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.7401</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5703</v>
+        <v>0.4116</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0769</v>
+        <v>0.3329</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6472</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.3729</v>
+        <v>-3.0202</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.3729</v>
+        <v>-3.0202</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. FIGUERAS LOPEZ</t>
+          <t>S. LITTLESON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.3181</v>
+        <v>-6.1861</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.2286</v>
+        <v>-4.5016</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0895</v>
+        <v>-1.6846</v>
       </c>
       <c r="G23" t="n">
-        <v>-7.1929</v>
+        <v>-4.8736</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2651</v>
+        <v>-4.68</v>
       </c>
       <c r="I23" t="n">
-        <v>-5.9278</v>
+        <v>-0.1936</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.7902</v>
+        <v>-2.7195</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6657</v>
+        <v>-3.9467</v>
       </c>
       <c r="L23" t="n">
-        <v>-4.1245</v>
+        <v>1.2272</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.4027</v>
+        <v>-2.1541</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5994</v>
+        <v>-0.7333</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.8033</v>
+        <v>-1.4208</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.209</v>
+        <v>-0.4224</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.4384</v>
+        <v>-0.6946</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2294</v>
+        <v>0.2722</v>
       </c>
       <c r="V23" t="n">
-        <v>0.4313</v>
+        <v>-1.3252</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.4313</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S. LITTLESON</t>
+          <t>P. FIGUERAS LOPEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.7725</v>
+        <v>-6.2583</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.5074</v>
+        <v>-5.4463</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.2651</v>
+        <v>-0.8121</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.8736</v>
+        <v>-7.1929</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.68</v>
+        <v>-1.2651</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1936</v>
+        <v>-5.9278</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.7195</v>
+        <v>-4.7902</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.9467</v>
+        <v>-0.6657</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2272</v>
+        <v>-4.1245</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.1541</v>
+        <v>-2.4027</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7333</v>
+        <v>-0.5994</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.4208</v>
+        <v>-1.8033</v>
       </c>
       <c r="P24" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.0087</v>
+        <v>-0.1493</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.7004</v>
+        <v>-0.6561</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3084</v>
+        <v>0.5068</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.3252</v>
+        <v>0.4313</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.3252</v>
+        <v>0.4313</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-23.9983</v>
+        <v>-23.253</v>
       </c>
       <c r="E25" t="n">
-        <v>-12.5553</v>
+        <v>-12.5554</v>
       </c>
       <c r="F25" t="n">
-        <v>-11.4429</v>
+        <v>-10.6979</v>
       </c>
       <c r="G25" t="n">
         <v>-23.0068</v>
@@ -2404,13 +2404,13 @@
         <v>8.699999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>1.7222</v>
+        <v>2.467</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.7449</v>
+        <v>-1.7448</v>
       </c>
       <c r="U25" t="n">
-        <v>3.4667</v>
+        <v>4.2118</v>
       </c>
       <c r="V25" t="n">
         <v>-3.801100000000001</v>
